--- a/artfynd/A 3798-2026 artfynd.xlsx
+++ b/artfynd/A 3798-2026 artfynd.xlsx
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187606</v>
+        <v>131187607</v>
       </c>
       <c r="B15" t="n">
         <v>57884</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440572</v>
+        <v>440597</v>
       </c>
       <c r="R15" t="n">
-        <v>7056973</v>
+        <v>7056955</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,7 +2285,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187607</v>
+        <v>131187606</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440597</v>
+        <v>440572</v>
       </c>
       <c r="R16" t="n">
-        <v>7056955</v>
+        <v>7056973</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 3798-2026 artfynd.xlsx
+++ b/artfynd/A 3798-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154928</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131154929</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131154930</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>131154931</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131154927</v>
       </c>
       <c r="B8" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131187624</v>
       </c>
       <c r="B9" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187607</v>
+        <v>131187606</v>
       </c>
       <c r="B15" t="n">
         <v>57884</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440597</v>
+        <v>440572</v>
       </c>
       <c r="R15" t="n">
-        <v>7056955</v>
+        <v>7056973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,7 +2285,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187606</v>
+        <v>131187607</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440572</v>
+        <v>440597</v>
       </c>
       <c r="R16" t="n">
-        <v>7056973</v>
+        <v>7056955</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 3798-2026 artfynd.xlsx
+++ b/artfynd/A 3798-2026 artfynd.xlsx
@@ -1452,7 +1452,7 @@
         <v>131154927</v>
       </c>
       <c r="B8" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131187624</v>
       </c>
       <c r="B9" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187606</v>
+        <v>131187607</v>
       </c>
       <c r="B15" t="n">
         <v>57884</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440572</v>
+        <v>440597</v>
       </c>
       <c r="R15" t="n">
-        <v>7056973</v>
+        <v>7056955</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,7 +2285,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187607</v>
+        <v>131187606</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440597</v>
+        <v>440572</v>
       </c>
       <c r="R16" t="n">
-        <v>7056955</v>
+        <v>7056973</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 3798-2026 artfynd.xlsx
+++ b/artfynd/A 3798-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154928</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131154929</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131154930</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>131154931</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131154927</v>
       </c>
       <c r="B8" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131187624</v>
       </c>
       <c r="B9" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187607</v>
+        <v>131187606</v>
       </c>
       <c r="B15" t="n">
         <v>57884</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440597</v>
+        <v>440572</v>
       </c>
       <c r="R15" t="n">
-        <v>7056955</v>
+        <v>7056973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,7 +2285,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187606</v>
+        <v>131187607</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440572</v>
+        <v>440597</v>
       </c>
       <c r="R16" t="n">
-        <v>7056973</v>
+        <v>7056955</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 3798-2026 artfynd.xlsx
+++ b/artfynd/A 3798-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154928</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131154929</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131154930</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>131154922</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>131154921</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>131154931</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131154927</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131187624</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131187605</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>131187602</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>131187603</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>131187610</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>131187608</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>131187606</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131187607</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>131187604</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>131187601</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>131187609</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 3798-2026 artfynd.xlsx
+++ b/artfynd/A 3798-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154928</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131154929</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131154930</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>131154922</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>131154921</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>131154931</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131154927</v>
       </c>
       <c r="B8" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131187624</v>
       </c>
       <c r="B9" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131187605</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>131187602</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>131187603</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>131187610</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>131187608</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>131187606</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131187607</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>131187604</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>131187601</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>131187609</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 3798-2026 artfynd.xlsx
+++ b/artfynd/A 3798-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154928</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131154929</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131154930</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>131154922</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>131154921</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>131154931</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131154927</v>
       </c>
       <c r="B8" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131187624</v>
       </c>
       <c r="B9" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131187605</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>131187602</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>131187603</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>131187610</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>131187608</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187606</v>
+        <v>131187607</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440572</v>
+        <v>440597</v>
       </c>
       <c r="R15" t="n">
-        <v>7056973</v>
+        <v>7056955</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187607</v>
+        <v>131187606</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440597</v>
+        <v>440572</v>
       </c>
       <c r="R16" t="n">
-        <v>7056955</v>
+        <v>7056973</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,7 +2390,7 @@
         <v>131187604</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>131187601</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>131187609</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 3798-2026 artfynd.xlsx
+++ b/artfynd/A 3798-2026 artfynd.xlsx
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187607</v>
+        <v>131187606</v>
       </c>
       <c r="B15" t="n">
         <v>57888</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440597</v>
+        <v>440572</v>
       </c>
       <c r="R15" t="n">
-        <v>7056955</v>
+        <v>7056973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,7 +2285,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187606</v>
+        <v>131187607</v>
       </c>
       <c r="B16" t="n">
         <v>57888</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440572</v>
+        <v>440597</v>
       </c>
       <c r="R16" t="n">
-        <v>7056973</v>
+        <v>7056955</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 3798-2026 artfynd.xlsx
+++ b/artfynd/A 3798-2026 artfynd.xlsx
@@ -1877,7 +1877,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187603</v>
+        <v>131187610</v>
       </c>
       <c r="B12" t="n">
         <v>57888</v>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440657</v>
+        <v>440688</v>
       </c>
       <c r="R12" t="n">
-        <v>7057019</v>
+        <v>7056887</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,7 +1979,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187610</v>
+        <v>131187603</v>
       </c>
       <c r="B13" t="n">
         <v>57888</v>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440688</v>
+        <v>440657</v>
       </c>
       <c r="R13" t="n">
-        <v>7056887</v>
+        <v>7057019</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 3798-2026 artfynd.xlsx
+++ b/artfynd/A 3798-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154928</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131154929</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131154930</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>131154922</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>131154921</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>131154931</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131154927</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131187624</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131187605</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>131187602</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>131187610</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>131187603</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>131187608</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187606</v>
+        <v>131187607</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440572</v>
+        <v>440597</v>
       </c>
       <c r="R15" t="n">
-        <v>7056973</v>
+        <v>7056955</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187607</v>
+        <v>131187606</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440597</v>
+        <v>440572</v>
       </c>
       <c r="R16" t="n">
-        <v>7056955</v>
+        <v>7056973</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,7 +2390,7 @@
         <v>131187604</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>131187601</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>131187609</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 3798-2026 artfynd.xlsx
+++ b/artfynd/A 3798-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154928</v>
       </c>
       <c r="B2" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131154929</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131154930</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>131154922</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>131154921</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>131154931</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131154927</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131187624</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131187605</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>131187602</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187610</v>
+        <v>131187603</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440688</v>
+        <v>440657</v>
       </c>
       <c r="R12" t="n">
-        <v>7056887</v>
+        <v>7057019</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187603</v>
+        <v>131187610</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440657</v>
+        <v>440688</v>
       </c>
       <c r="R13" t="n">
-        <v>7057019</v>
+        <v>7056887</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,7 +2084,7 @@
         <v>131187608</v>
       </c>
       <c r="B14" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187607</v>
+        <v>131187606</v>
       </c>
       <c r="B15" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440597</v>
+        <v>440572</v>
       </c>
       <c r="R15" t="n">
-        <v>7056955</v>
+        <v>7056973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187606</v>
+        <v>131187607</v>
       </c>
       <c r="B16" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440572</v>
+        <v>440597</v>
       </c>
       <c r="R16" t="n">
-        <v>7056973</v>
+        <v>7056955</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,7 +2390,7 @@
         <v>131187604</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>131187601</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>131187609</v>
       </c>
       <c r="B19" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 3798-2026 artfynd.xlsx
+++ b/artfynd/A 3798-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154928</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131154929</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131154930</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>131154922</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>131154921</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>131154931</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131154927</v>
       </c>
       <c r="B8" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131187624</v>
       </c>
       <c r="B9" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131187605</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>131187602</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>131187603</v>
       </c>
       <c r="B12" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>131187610</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>131187608</v>
       </c>
       <c r="B14" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>131187606</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131187607</v>
       </c>
       <c r="B16" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>131187604</v>
       </c>
       <c r="B17" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>131187601</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>131187609</v>
       </c>
       <c r="B19" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
